--- a/print.xlsx
+++ b/print.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d30ae142562e1ddc/보험/한화라이프랩/자동화 프로그램 모음/bojang-v3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d30ae142562e1ddc/보험/한화라이프랩/자동화 프로그램 모음/insurance_tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{567D7A04-6FFF-4426-A8EA-D3603580CD44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A93962C3-4111-4948-A09A-735D5C66E3C0}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{567D7A04-6FFF-4426-A8EA-D3603580CD44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6790A90D-C612-437B-B37F-61941F759F79}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기존 보험" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'기존 보험'!$A$1:$R$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'기존 보험'!$A$1:$AB$49</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -330,7 +330,7 @@
     <numFmt numFmtId="178" formatCode="#,##0&quot;만&quot;&quot;원&quot;&quot; &quot;;\-#,##0&quot; &quot;;"/>
     <numFmt numFmtId="179" formatCode="###,###,###,###&quot;만원&quot;"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -401,6 +401,22 @@
       <b/>
       <vertAlign val="superscript"/>
       <sz val="72"/>
+      <color rgb="FF000000"/>
+      <name val="나눔고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="48"/>
+      <color rgb="FF0000FF"/>
+      <name val="나눔고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="48"/>
       <color rgb="FF000000"/>
       <name val="나눔고딕"/>
       <family val="3"/>
@@ -895,133 +911,46 @@
     <xf numFmtId="177" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="8" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="8" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="8" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1033,34 +962,19 @@
     <xf numFmtId="49" fontId="8" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1069,37 +983,26 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="177" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1108,9 +1011,14 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1122,6 +1030,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1129,31 +1040,136 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="10" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="8" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1414,10 +1430,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1744,45 +1756,55 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R52"/>
+  <dimension ref="A1:AB52"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="47.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="83.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="31.625" style="1" customWidth="1"/>
     <col min="3" max="3" width="84.625" style="1" customWidth="1"/>
-    <col min="4" max="18" width="75.625" style="1" customWidth="1"/>
-    <col min="19" max="22" width="8.75" style="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.75" style="1"/>
+    <col min="4" max="28" width="75.625" style="1" customWidth="1"/>
+    <col min="29" max="32" width="8.75" style="1" customWidth="1"/>
+    <col min="33" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="274.5" customHeight="1" thickBot="1" x14ac:dyDescent="1.2">
-      <c r="A1" s="76"/>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63"/>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
-      <c r="R1" s="63"/>
-    </row>
-    <row r="2" spans="1:18" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="80" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="68" t="s">
+    <row r="1" spans="1:28" ht="274.5" customHeight="1" thickBot="1" x14ac:dyDescent="1.2">
+      <c r="A1" s="37"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="29"/>
+    </row>
+    <row r="2" spans="1:28" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="45" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="2"/>
@@ -1800,11 +1822,21 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
-    </row>
-    <row r="3" spans="1:18" ht="120" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="82"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+    </row>
+    <row r="3" spans="1:28" ht="120" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="43"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="46"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -1820,13 +1852,23 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
-    </row>
-    <row r="4" spans="1:18" ht="80.099999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="70" t="s">
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+    </row>
+    <row r="4" spans="1:28" ht="80.099999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="72"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -1842,13 +1884,23 @@
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
-    </row>
-    <row r="5" spans="1:18" ht="80.099999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="73" t="s">
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4"/>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="4"/>
+    </row>
+    <row r="5" spans="1:28" ht="80.099999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="75"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -1864,13 +1916,23 @@
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
-    </row>
-    <row r="6" spans="1:18" ht="80.099999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="73" t="s">
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
+      <c r="Z5" s="5"/>
+      <c r="AA5" s="5"/>
+      <c r="AB5" s="5"/>
+    </row>
+    <row r="6" spans="1:28" ht="80.099999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="74"/>
-      <c r="C6" s="75"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="61"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -1886,1169 +1948,1645 @@
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
-    </row>
-    <row r="7" spans="1:18" ht="80.099999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="64">
-        <f t="shared" ref="A7:A48" si="0">SUM(D7:R7)</f>
-        <v>0</v>
-      </c>
-      <c r="B7" s="95" t="s">
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5"/>
+      <c r="AA6" s="5"/>
+      <c r="AB6" s="5"/>
+    </row>
+    <row r="7" spans="1:28" ht="80.099999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="63">
+        <f t="shared" ref="A7:A48" si="0">SUM(D7:AB7)</f>
+        <v>0</v>
+      </c>
+      <c r="B7" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="96"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-    </row>
-    <row r="8" spans="1:18" ht="80.099999999999994" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B8" s="83" t="s">
+      <c r="C7" s="54"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="62"/>
+      <c r="N7" s="62"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="62"/>
+      <c r="Q7" s="62"/>
+      <c r="R7" s="62"/>
+      <c r="S7" s="62"/>
+      <c r="T7" s="62"/>
+      <c r="U7" s="62"/>
+      <c r="V7" s="62"/>
+      <c r="W7" s="62"/>
+      <c r="X7" s="62"/>
+      <c r="Y7" s="62"/>
+      <c r="Z7" s="62"/>
+      <c r="AA7" s="62"/>
+      <c r="AB7" s="62"/>
+    </row>
+    <row r="8" spans="1:28" ht="80.099999999999994" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B8" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="84"/>
-      <c r="D8" s="90"/>
-      <c r="E8" s="91"/>
-      <c r="F8" s="91"/>
-      <c r="G8" s="91"/>
-      <c r="H8" s="91"/>
-      <c r="I8" s="91"/>
-      <c r="J8" s="91"/>
-      <c r="K8" s="91"/>
-      <c r="L8" s="91"/>
-      <c r="M8" s="91"/>
-      <c r="N8" s="91"/>
-      <c r="O8" s="91"/>
-      <c r="P8" s="91"/>
-      <c r="Q8" s="91"/>
-      <c r="R8" s="91"/>
-    </row>
-    <row r="9" spans="1:18" ht="80.099999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B9" s="85" t="s">
+      <c r="C8" s="48"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="33"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="33"/>
+      <c r="O8" s="33"/>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="33"/>
+      <c r="R8" s="33"/>
+      <c r="S8" s="33"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="33"/>
+      <c r="V8" s="33"/>
+      <c r="W8" s="33"/>
+      <c r="X8" s="33"/>
+      <c r="Y8" s="33"/>
+      <c r="Z8" s="33"/>
+      <c r="AA8" s="33"/>
+      <c r="AB8" s="33"/>
+    </row>
+    <row r="9" spans="1:28" ht="80.099999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B9" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="86"/>
-      <c r="D9" s="92"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="93"/>
-      <c r="J9" s="93"/>
-      <c r="K9" s="93"/>
-      <c r="L9" s="93"/>
-      <c r="M9" s="93"/>
-      <c r="N9" s="93"/>
-      <c r="O9" s="93"/>
-      <c r="P9" s="93"/>
-      <c r="Q9" s="93"/>
-      <c r="R9" s="93"/>
-    </row>
-    <row r="10" spans="1:18" ht="80.099999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="89">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B10" s="85" t="s">
+      <c r="C9" s="51"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="35"/>
+      <c r="Q9" s="35"/>
+      <c r="R9" s="35"/>
+      <c r="S9" s="35"/>
+      <c r="T9" s="35"/>
+      <c r="U9" s="35"/>
+      <c r="V9" s="35"/>
+      <c r="W9" s="35"/>
+      <c r="X9" s="35"/>
+      <c r="Y9" s="35"/>
+      <c r="Z9" s="35"/>
+      <c r="AA9" s="35"/>
+      <c r="AB9" s="35"/>
+    </row>
+    <row r="10" spans="1:28" ht="80.099999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B10" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="86"/>
-      <c r="D10" s="94"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="94"/>
-      <c r="J10" s="94"/>
-      <c r="K10" s="94"/>
-      <c r="L10" s="94"/>
-      <c r="M10" s="94"/>
-      <c r="N10" s="94"/>
-      <c r="O10" s="94"/>
-      <c r="P10" s="94"/>
-      <c r="Q10" s="94"/>
-      <c r="R10" s="94"/>
-    </row>
-    <row r="11" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B11" s="87" t="s">
+      <c r="C10" s="51"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="36"/>
+      <c r="L10" s="36"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
+      <c r="S10" s="36"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="36"/>
+      <c r="V10" s="36"/>
+      <c r="W10" s="36"/>
+      <c r="X10" s="36"/>
+      <c r="Y10" s="36"/>
+      <c r="Z10" s="36"/>
+      <c r="AA10" s="36"/>
+      <c r="AB10" s="36"/>
+    </row>
+    <row r="11" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B11" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-    </row>
-    <row r="12" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="11" t="s">
+      <c r="D11" s="80"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="80"/>
+      <c r="K11" s="80"/>
+      <c r="L11" s="80"/>
+      <c r="M11" s="80"/>
+      <c r="N11" s="80"/>
+      <c r="O11" s="80"/>
+      <c r="P11" s="80"/>
+      <c r="Q11" s="80"/>
+      <c r="R11" s="80"/>
+      <c r="S11" s="80"/>
+      <c r="T11" s="80"/>
+      <c r="U11" s="80"/>
+      <c r="V11" s="80"/>
+      <c r="W11" s="80"/>
+      <c r="X11" s="80"/>
+      <c r="Y11" s="80"/>
+      <c r="Z11" s="80"/>
+      <c r="AA11" s="80"/>
+      <c r="AB11" s="80"/>
+    </row>
+    <row r="12" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="65">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B12" s="40"/>
+      <c r="C12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-    </row>
-    <row r="13" spans="1:18" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="14" t="s">
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="81"/>
+      <c r="K12" s="81"/>
+      <c r="L12" s="81"/>
+      <c r="M12" s="81"/>
+      <c r="N12" s="81"/>
+      <c r="O12" s="81"/>
+      <c r="P12" s="81"/>
+      <c r="Q12" s="81"/>
+      <c r="R12" s="81"/>
+      <c r="S12" s="81"/>
+      <c r="T12" s="81"/>
+      <c r="U12" s="81"/>
+      <c r="V12" s="81"/>
+      <c r="W12" s="81"/>
+      <c r="X12" s="81"/>
+      <c r="Y12" s="81"/>
+      <c r="Z12" s="81"/>
+      <c r="AA12" s="81"/>
+      <c r="AB12" s="81"/>
+    </row>
+    <row r="13" spans="1:28" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="66">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B13" s="40"/>
+      <c r="C13" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
-    </row>
-    <row r="14" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B14" s="65" t="s">
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="82"/>
+      <c r="K13" s="82"/>
+      <c r="L13" s="82"/>
+      <c r="M13" s="82"/>
+      <c r="N13" s="82"/>
+      <c r="O13" s="82"/>
+      <c r="P13" s="82"/>
+      <c r="Q13" s="82"/>
+      <c r="R13" s="82"/>
+      <c r="S13" s="82"/>
+      <c r="T13" s="82"/>
+      <c r="U13" s="82"/>
+      <c r="V13" s="82"/>
+      <c r="W13" s="82"/>
+      <c r="X13" s="82"/>
+      <c r="Y13" s="82"/>
+      <c r="Z13" s="82"/>
+      <c r="AA13" s="82"/>
+      <c r="AB13" s="82"/>
+    </row>
+    <row r="14" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="67">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B14" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="18"/>
-      <c r="R14" s="18"/>
-    </row>
-    <row r="15" spans="1:18" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B15" s="67"/>
-      <c r="C15" s="20" t="s">
+      <c r="D14" s="83"/>
+      <c r="E14" s="83"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="83"/>
+      <c r="J14" s="83"/>
+      <c r="K14" s="83"/>
+      <c r="L14" s="83"/>
+      <c r="M14" s="83"/>
+      <c r="N14" s="83"/>
+      <c r="O14" s="83"/>
+      <c r="P14" s="83"/>
+      <c r="Q14" s="83"/>
+      <c r="R14" s="83"/>
+      <c r="S14" s="83"/>
+      <c r="T14" s="83"/>
+      <c r="U14" s="83"/>
+      <c r="V14" s="83"/>
+      <c r="W14" s="83"/>
+      <c r="X14" s="83"/>
+      <c r="Y14" s="83"/>
+      <c r="Z14" s="83"/>
+      <c r="AA14" s="83"/>
+      <c r="AB14" s="83"/>
+    </row>
+    <row r="15" spans="1:28" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="68">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B15" s="43"/>
+      <c r="C15" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
-    </row>
-    <row r="16" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B16" s="78" t="s">
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="84"/>
+      <c r="N15" s="84"/>
+      <c r="O15" s="84"/>
+      <c r="P15" s="84"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="84"/>
+      <c r="S15" s="84"/>
+      <c r="T15" s="84"/>
+      <c r="U15" s="84"/>
+      <c r="V15" s="84"/>
+      <c r="W15" s="84"/>
+      <c r="X15" s="84"/>
+      <c r="Y15" s="84"/>
+      <c r="Z15" s="84"/>
+      <c r="AA15" s="84"/>
+      <c r="AB15" s="84"/>
+    </row>
+    <row r="16" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B16" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="24"/>
-    </row>
-    <row r="17" spans="1:18" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B17" s="66"/>
-      <c r="C17" s="26" t="s">
+      <c r="D16" s="85"/>
+      <c r="E16" s="85"/>
+      <c r="F16" s="85"/>
+      <c r="G16" s="85"/>
+      <c r="H16" s="85"/>
+      <c r="I16" s="85"/>
+      <c r="J16" s="85"/>
+      <c r="K16" s="85"/>
+      <c r="L16" s="85"/>
+      <c r="M16" s="85"/>
+      <c r="N16" s="85"/>
+      <c r="O16" s="85"/>
+      <c r="P16" s="85"/>
+      <c r="Q16" s="85"/>
+      <c r="R16" s="85"/>
+      <c r="S16" s="85"/>
+      <c r="T16" s="85"/>
+      <c r="U16" s="85"/>
+      <c r="V16" s="85"/>
+      <c r="W16" s="85"/>
+      <c r="X16" s="85"/>
+      <c r="Y16" s="85"/>
+      <c r="Z16" s="85"/>
+      <c r="AA16" s="85"/>
+      <c r="AB16" s="85"/>
+    </row>
+    <row r="17" spans="1:28" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="70">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B17" s="40"/>
+      <c r="C17" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="27"/>
-      <c r="M17" s="27"/>
-      <c r="N17" s="27"/>
-      <c r="O17" s="27"/>
-      <c r="P17" s="27"/>
-      <c r="Q17" s="27"/>
-      <c r="R17" s="27"/>
-    </row>
-    <row r="18" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B18" s="65" t="s">
+      <c r="D17" s="86"/>
+      <c r="E17" s="86"/>
+      <c r="F17" s="86"/>
+      <c r="G17" s="86"/>
+      <c r="H17" s="86"/>
+      <c r="I17" s="86"/>
+      <c r="J17" s="86"/>
+      <c r="K17" s="86"/>
+      <c r="L17" s="86"/>
+      <c r="M17" s="86"/>
+      <c r="N17" s="86"/>
+      <c r="O17" s="86"/>
+      <c r="P17" s="86"/>
+      <c r="Q17" s="86"/>
+      <c r="R17" s="86"/>
+      <c r="S17" s="86"/>
+      <c r="T17" s="86"/>
+      <c r="U17" s="86"/>
+      <c r="V17" s="86"/>
+      <c r="W17" s="86"/>
+      <c r="X17" s="86"/>
+      <c r="Y17" s="86"/>
+      <c r="Z17" s="86"/>
+      <c r="AA17" s="86"/>
+      <c r="AB17" s="86"/>
+    </row>
+    <row r="18" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="71">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B18" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="30"/>
-      <c r="O18" s="30"/>
-      <c r="P18" s="30"/>
-      <c r="Q18" s="30"/>
-      <c r="R18" s="30"/>
-    </row>
-    <row r="19" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B19" s="66"/>
-      <c r="C19" s="32" t="s">
+      <c r="D18" s="87"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="87"/>
+      <c r="I18" s="87"/>
+      <c r="J18" s="87"/>
+      <c r="K18" s="87"/>
+      <c r="L18" s="87"/>
+      <c r="M18" s="87"/>
+      <c r="N18" s="87"/>
+      <c r="O18" s="87"/>
+      <c r="P18" s="87"/>
+      <c r="Q18" s="87"/>
+      <c r="R18" s="87"/>
+      <c r="S18" s="87"/>
+      <c r="T18" s="87"/>
+      <c r="U18" s="87"/>
+      <c r="V18" s="87"/>
+      <c r="W18" s="87"/>
+      <c r="X18" s="87"/>
+      <c r="Y18" s="87"/>
+      <c r="Z18" s="87"/>
+      <c r="AA18" s="87"/>
+      <c r="AB18" s="87"/>
+    </row>
+    <row r="19" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="72">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B19" s="40"/>
+      <c r="C19" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="33"/>
-      <c r="O19" s="33"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="33"/>
-      <c r="R19" s="33"/>
-    </row>
-    <row r="20" spans="1:18" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B20" s="67"/>
-      <c r="C20" s="35" t="s">
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="88"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="88"/>
+      <c r="J19" s="88"/>
+      <c r="K19" s="88"/>
+      <c r="L19" s="88"/>
+      <c r="M19" s="88"/>
+      <c r="N19" s="88"/>
+      <c r="O19" s="88"/>
+      <c r="P19" s="88"/>
+      <c r="Q19" s="88"/>
+      <c r="R19" s="88"/>
+      <c r="S19" s="88"/>
+      <c r="T19" s="88"/>
+      <c r="U19" s="88"/>
+      <c r="V19" s="88"/>
+      <c r="W19" s="88"/>
+      <c r="X19" s="88"/>
+      <c r="Y19" s="88"/>
+      <c r="Z19" s="88"/>
+      <c r="AA19" s="88"/>
+      <c r="AB19" s="88"/>
+    </row>
+    <row r="20" spans="1:28" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="73">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B20" s="43"/>
+      <c r="C20" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="36"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="36"/>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
-    </row>
-    <row r="21" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B21" s="65" t="s">
+      <c r="D20" s="89"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="89"/>
+      <c r="I20" s="89"/>
+      <c r="J20" s="89"/>
+      <c r="K20" s="89"/>
+      <c r="L20" s="89"/>
+      <c r="M20" s="89"/>
+      <c r="N20" s="89"/>
+      <c r="O20" s="89"/>
+      <c r="P20" s="89"/>
+      <c r="Q20" s="89"/>
+      <c r="R20" s="89"/>
+      <c r="S20" s="89"/>
+      <c r="T20" s="89"/>
+      <c r="U20" s="89"/>
+      <c r="V20" s="89"/>
+      <c r="W20" s="89"/>
+      <c r="X20" s="89"/>
+      <c r="Y20" s="89"/>
+      <c r="Z20" s="89"/>
+      <c r="AA20" s="89"/>
+      <c r="AB20" s="89"/>
+    </row>
+    <row r="21" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="74">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B21" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="39"/>
-      <c r="L21" s="39"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="39"/>
-      <c r="O21" s="39"/>
-      <c r="P21" s="39"/>
-      <c r="Q21" s="39"/>
-      <c r="R21" s="39"/>
-    </row>
-    <row r="22" spans="1:18" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B22" s="67"/>
-      <c r="C22" s="41" t="s">
+      <c r="D21" s="90"/>
+      <c r="E21" s="90"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="90"/>
+      <c r="I21" s="90"/>
+      <c r="J21" s="90"/>
+      <c r="K21" s="90"/>
+      <c r="L21" s="90"/>
+      <c r="M21" s="90"/>
+      <c r="N21" s="90"/>
+      <c r="O21" s="90"/>
+      <c r="P21" s="90"/>
+      <c r="Q21" s="90"/>
+      <c r="R21" s="90"/>
+      <c r="S21" s="90"/>
+      <c r="T21" s="90"/>
+      <c r="U21" s="90"/>
+      <c r="V21" s="90"/>
+      <c r="W21" s="90"/>
+      <c r="X21" s="90"/>
+      <c r="Y21" s="90"/>
+      <c r="Z21" s="90"/>
+      <c r="AA21" s="90"/>
+      <c r="AB21" s="90"/>
+    </row>
+    <row r="22" spans="1:28" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B22" s="43"/>
+      <c r="C22" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="42"/>
-      <c r="J22" s="42"/>
-      <c r="K22" s="42"/>
-      <c r="L22" s="42"/>
-      <c r="M22" s="42"/>
-      <c r="N22" s="42"/>
-      <c r="O22" s="42"/>
-      <c r="P22" s="42"/>
-      <c r="Q22" s="42"/>
-      <c r="R22" s="42"/>
-    </row>
-    <row r="23" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B23" s="69" t="s">
+      <c r="D22" s="91"/>
+      <c r="E22" s="91"/>
+      <c r="F22" s="91"/>
+      <c r="G22" s="91"/>
+      <c r="H22" s="91"/>
+      <c r="I22" s="91"/>
+      <c r="J22" s="91"/>
+      <c r="K22" s="91"/>
+      <c r="L22" s="91"/>
+      <c r="M22" s="91"/>
+      <c r="N22" s="91"/>
+      <c r="O22" s="91"/>
+      <c r="P22" s="91"/>
+      <c r="Q22" s="91"/>
+      <c r="R22" s="91"/>
+      <c r="S22" s="91"/>
+      <c r="T22" s="91"/>
+      <c r="U22" s="91"/>
+      <c r="V22" s="91"/>
+      <c r="W22" s="91"/>
+      <c r="X22" s="91"/>
+      <c r="Y22" s="91"/>
+      <c r="Z22" s="91"/>
+      <c r="AA22" s="91"/>
+      <c r="AB22" s="91"/>
+    </row>
+    <row r="23" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="67">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B23" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
-      <c r="P23" s="18"/>
-      <c r="Q23" s="18"/>
-      <c r="R23" s="18"/>
-    </row>
-    <row r="24" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B24" s="66"/>
-      <c r="C24" s="44" t="s">
+      <c r="D23" s="83"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
+      <c r="H23" s="83"/>
+      <c r="I23" s="83"/>
+      <c r="J23" s="83"/>
+      <c r="K23" s="83"/>
+      <c r="L23" s="83"/>
+      <c r="M23" s="83"/>
+      <c r="N23" s="83"/>
+      <c r="O23" s="83"/>
+      <c r="P23" s="83"/>
+      <c r="Q23" s="83"/>
+      <c r="R23" s="83"/>
+      <c r="S23" s="83"/>
+      <c r="T23" s="83"/>
+      <c r="U23" s="83"/>
+      <c r="V23" s="83"/>
+      <c r="W23" s="83"/>
+      <c r="X23" s="83"/>
+      <c r="Y23" s="83"/>
+      <c r="Z23" s="83"/>
+      <c r="AA23" s="83"/>
+      <c r="AB23" s="83"/>
+    </row>
+    <row r="24" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B24" s="40"/>
+      <c r="C24" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="45"/>
-      <c r="M24" s="45"/>
-      <c r="N24" s="45"/>
-      <c r="O24" s="45"/>
-      <c r="P24" s="45"/>
-      <c r="Q24" s="45"/>
-      <c r="R24" s="45"/>
-    </row>
-    <row r="25" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B25" s="66"/>
-      <c r="C25" s="44" t="s">
+      <c r="D24" s="92"/>
+      <c r="E24" s="92"/>
+      <c r="F24" s="92"/>
+      <c r="G24" s="92"/>
+      <c r="H24" s="92"/>
+      <c r="I24" s="92"/>
+      <c r="J24" s="92"/>
+      <c r="K24" s="92"/>
+      <c r="L24" s="92"/>
+      <c r="M24" s="92"/>
+      <c r="N24" s="92"/>
+      <c r="O24" s="92"/>
+      <c r="P24" s="92"/>
+      <c r="Q24" s="92"/>
+      <c r="R24" s="92"/>
+      <c r="S24" s="92"/>
+      <c r="T24" s="92"/>
+      <c r="U24" s="92"/>
+      <c r="V24" s="92"/>
+      <c r="W24" s="92"/>
+      <c r="X24" s="92"/>
+      <c r="Y24" s="92"/>
+      <c r="Z24" s="92"/>
+      <c r="AA24" s="92"/>
+      <c r="AB24" s="92"/>
+    </row>
+    <row r="25" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B25" s="40"/>
+      <c r="C25" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="45"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="45"/>
-      <c r="M25" s="45"/>
-      <c r="N25" s="45"/>
-      <c r="O25" s="45"/>
-      <c r="P25" s="45"/>
-      <c r="Q25" s="45"/>
-      <c r="R25" s="45"/>
-    </row>
-    <row r="26" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B26" s="66"/>
-      <c r="C26" s="44" t="s">
+      <c r="D25" s="92"/>
+      <c r="E25" s="92"/>
+      <c r="F25" s="92"/>
+      <c r="G25" s="92"/>
+      <c r="H25" s="92"/>
+      <c r="I25" s="92"/>
+      <c r="J25" s="92"/>
+      <c r="K25" s="92"/>
+      <c r="L25" s="92"/>
+      <c r="M25" s="92"/>
+      <c r="N25" s="92"/>
+      <c r="O25" s="92"/>
+      <c r="P25" s="92"/>
+      <c r="Q25" s="92"/>
+      <c r="R25" s="92"/>
+      <c r="S25" s="92"/>
+      <c r="T25" s="92"/>
+      <c r="U25" s="92"/>
+      <c r="V25" s="92"/>
+      <c r="W25" s="92"/>
+      <c r="X25" s="92"/>
+      <c r="Y25" s="92"/>
+      <c r="Z25" s="92"/>
+      <c r="AA25" s="92"/>
+      <c r="AB25" s="92"/>
+    </row>
+    <row r="26" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B26" s="40"/>
+      <c r="C26" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="45"/>
-      <c r="M26" s="45"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="45"/>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="45"/>
-      <c r="R26" s="45"/>
-    </row>
-    <row r="27" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B27" s="66"/>
-      <c r="C27" s="44" t="s">
+      <c r="D26" s="92"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="92"/>
+      <c r="G26" s="92"/>
+      <c r="H26" s="92"/>
+      <c r="I26" s="92"/>
+      <c r="J26" s="92"/>
+      <c r="K26" s="92"/>
+      <c r="L26" s="92"/>
+      <c r="M26" s="92"/>
+      <c r="N26" s="92"/>
+      <c r="O26" s="92"/>
+      <c r="P26" s="92"/>
+      <c r="Q26" s="92"/>
+      <c r="R26" s="92"/>
+      <c r="S26" s="92"/>
+      <c r="T26" s="92"/>
+      <c r="U26" s="92"/>
+      <c r="V26" s="92"/>
+      <c r="W26" s="92"/>
+      <c r="X26" s="92"/>
+      <c r="Y26" s="92"/>
+      <c r="Z26" s="92"/>
+      <c r="AA26" s="92"/>
+      <c r="AB26" s="92"/>
+    </row>
+    <row r="27" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B27" s="40"/>
+      <c r="C27" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="45"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="45"/>
-      <c r="M27" s="45"/>
-      <c r="N27" s="45"/>
-      <c r="O27" s="45"/>
-      <c r="P27" s="45"/>
-      <c r="Q27" s="45"/>
-      <c r="R27" s="45"/>
-    </row>
-    <row r="28" spans="1:18" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="46">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B28" s="67"/>
-      <c r="C28" s="20" t="s">
+      <c r="D27" s="92"/>
+      <c r="E27" s="92"/>
+      <c r="F27" s="92"/>
+      <c r="G27" s="92"/>
+      <c r="H27" s="92"/>
+      <c r="I27" s="92"/>
+      <c r="J27" s="92"/>
+      <c r="K27" s="92"/>
+      <c r="L27" s="92"/>
+      <c r="M27" s="92"/>
+      <c r="N27" s="92"/>
+      <c r="O27" s="92"/>
+      <c r="P27" s="92"/>
+      <c r="Q27" s="92"/>
+      <c r="R27" s="92"/>
+      <c r="S27" s="92"/>
+      <c r="T27" s="92"/>
+      <c r="U27" s="92"/>
+      <c r="V27" s="92"/>
+      <c r="W27" s="92"/>
+      <c r="X27" s="92"/>
+      <c r="Y27" s="92"/>
+      <c r="Z27" s="92"/>
+      <c r="AA27" s="92"/>
+      <c r="AB27" s="92"/>
+    </row>
+    <row r="28" spans="1:28" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B28" s="43"/>
+      <c r="C28" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
-      <c r="O28" s="21"/>
-      <c r="P28" s="21"/>
-      <c r="Q28" s="21"/>
-      <c r="R28" s="21"/>
-    </row>
-    <row r="29" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B29" s="69" t="s">
+      <c r="D28" s="84"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="84"/>
+      <c r="G28" s="84"/>
+      <c r="H28" s="84"/>
+      <c r="I28" s="84"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
+      <c r="M28" s="84"/>
+      <c r="N28" s="84"/>
+      <c r="O28" s="84"/>
+      <c r="P28" s="84"/>
+      <c r="Q28" s="84"/>
+      <c r="R28" s="84"/>
+      <c r="S28" s="84"/>
+      <c r="T28" s="84"/>
+      <c r="U28" s="84"/>
+      <c r="V28" s="84"/>
+      <c r="W28" s="84"/>
+      <c r="X28" s="84"/>
+      <c r="Y28" s="84"/>
+      <c r="Z28" s="84"/>
+      <c r="AA28" s="84"/>
+      <c r="AB28" s="84"/>
+    </row>
+    <row r="29" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="67">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B29" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="18"/>
-      <c r="N29" s="18"/>
-      <c r="O29" s="18"/>
-      <c r="P29" s="18"/>
-      <c r="Q29" s="18"/>
-      <c r="R29" s="18"/>
-    </row>
-    <row r="30" spans="1:18" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B30" s="67"/>
-      <c r="C30" s="20" t="s">
+      <c r="D29" s="83"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="83"/>
+      <c r="H29" s="83"/>
+      <c r="I29" s="83"/>
+      <c r="J29" s="83"/>
+      <c r="K29" s="83"/>
+      <c r="L29" s="83"/>
+      <c r="M29" s="83"/>
+      <c r="N29" s="83"/>
+      <c r="O29" s="83"/>
+      <c r="P29" s="83"/>
+      <c r="Q29" s="83"/>
+      <c r="R29" s="83"/>
+      <c r="S29" s="83"/>
+      <c r="T29" s="83"/>
+      <c r="U29" s="83"/>
+      <c r="V29" s="83"/>
+      <c r="W29" s="83"/>
+      <c r="X29" s="83"/>
+      <c r="Y29" s="83"/>
+      <c r="Z29" s="83"/>
+      <c r="AA29" s="83"/>
+      <c r="AB29" s="83"/>
+    </row>
+    <row r="30" spans="1:28" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="68">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B30" s="43"/>
+      <c r="C30" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
-      <c r="O30" s="21"/>
-      <c r="P30" s="21"/>
-      <c r="Q30" s="21"/>
-      <c r="R30" s="21"/>
-    </row>
-    <row r="31" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B31" s="65" t="s">
+      <c r="D30" s="84"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="84"/>
+      <c r="O30" s="84"/>
+      <c r="P30" s="84"/>
+      <c r="Q30" s="84"/>
+      <c r="R30" s="84"/>
+      <c r="S30" s="84"/>
+      <c r="T30" s="84"/>
+      <c r="U30" s="84"/>
+      <c r="V30" s="84"/>
+      <c r="W30" s="84"/>
+      <c r="X30" s="84"/>
+      <c r="Y30" s="84"/>
+      <c r="Z30" s="84"/>
+      <c r="AA30" s="84"/>
+      <c r="AB30" s="84"/>
+    </row>
+    <row r="31" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="67">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B31" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="47" t="s">
+      <c r="C31" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="18"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="18"/>
-      <c r="M31" s="18"/>
-      <c r="N31" s="18"/>
-      <c r="O31" s="18"/>
-      <c r="P31" s="18"/>
-      <c r="Q31" s="18"/>
-      <c r="R31" s="18"/>
-    </row>
-    <row r="32" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B32" s="66"/>
-      <c r="C32" s="8" t="s">
+      <c r="D31" s="83"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="83"/>
+      <c r="G31" s="83"/>
+      <c r="H31" s="83"/>
+      <c r="I31" s="83"/>
+      <c r="J31" s="83"/>
+      <c r="K31" s="83"/>
+      <c r="L31" s="83"/>
+      <c r="M31" s="83"/>
+      <c r="N31" s="83"/>
+      <c r="O31" s="83"/>
+      <c r="P31" s="83"/>
+      <c r="Q31" s="83"/>
+      <c r="R31" s="83"/>
+      <c r="S31" s="83"/>
+      <c r="T31" s="83"/>
+      <c r="U31" s="83"/>
+      <c r="V31" s="83"/>
+      <c r="W31" s="83"/>
+      <c r="X31" s="83"/>
+      <c r="Y31" s="83"/>
+      <c r="Z31" s="83"/>
+      <c r="AA31" s="83"/>
+      <c r="AB31" s="83"/>
+    </row>
+    <row r="32" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B32" s="40"/>
+      <c r="C32" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="48"/>
-      <c r="J32" s="48"/>
-      <c r="K32" s="48"/>
-      <c r="L32" s="48"/>
-      <c r="M32" s="48"/>
-      <c r="N32" s="48"/>
-      <c r="O32" s="48"/>
-      <c r="P32" s="48"/>
-      <c r="Q32" s="48"/>
-      <c r="R32" s="48"/>
-    </row>
-    <row r="33" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B33" s="66"/>
-      <c r="C33" s="11" t="s">
+      <c r="D32" s="93"/>
+      <c r="E32" s="93"/>
+      <c r="F32" s="93"/>
+      <c r="G32" s="93"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="93"/>
+      <c r="J32" s="93"/>
+      <c r="K32" s="93"/>
+      <c r="L32" s="93"/>
+      <c r="M32" s="93"/>
+      <c r="N32" s="93"/>
+      <c r="O32" s="93"/>
+      <c r="P32" s="93"/>
+      <c r="Q32" s="93"/>
+      <c r="R32" s="93"/>
+      <c r="S32" s="93"/>
+      <c r="T32" s="93"/>
+      <c r="U32" s="93"/>
+      <c r="V32" s="93"/>
+      <c r="W32" s="93"/>
+      <c r="X32" s="93"/>
+      <c r="Y32" s="93"/>
+      <c r="Z32" s="93"/>
+      <c r="AA32" s="93"/>
+      <c r="AB32" s="93"/>
+    </row>
+    <row r="33" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="65">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B33" s="40"/>
+      <c r="C33" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="12"/>
-      <c r="P33" s="12"/>
-      <c r="Q33" s="12"/>
-      <c r="R33" s="12"/>
-    </row>
-    <row r="34" spans="1:18" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B34" s="67"/>
-      <c r="C34" s="20" t="s">
+      <c r="D33" s="81"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="81"/>
+      <c r="H33" s="81"/>
+      <c r="I33" s="81"/>
+      <c r="J33" s="81"/>
+      <c r="K33" s="81"/>
+      <c r="L33" s="81"/>
+      <c r="M33" s="81"/>
+      <c r="N33" s="81"/>
+      <c r="O33" s="81"/>
+      <c r="P33" s="81"/>
+      <c r="Q33" s="81"/>
+      <c r="R33" s="81"/>
+      <c r="S33" s="81"/>
+      <c r="T33" s="81"/>
+      <c r="U33" s="81"/>
+      <c r="V33" s="81"/>
+      <c r="W33" s="81"/>
+      <c r="X33" s="81"/>
+      <c r="Y33" s="81"/>
+      <c r="Z33" s="81"/>
+      <c r="AA33" s="81"/>
+      <c r="AB33" s="81"/>
+    </row>
+    <row r="34" spans="1:28" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="68">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B34" s="43"/>
+      <c r="C34" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="21"/>
-      <c r="K34" s="21"/>
-      <c r="L34" s="21"/>
-      <c r="M34" s="21"/>
-      <c r="N34" s="21"/>
-      <c r="O34" s="21"/>
-      <c r="P34" s="21"/>
-      <c r="Q34" s="21"/>
-      <c r="R34" s="21"/>
-    </row>
-    <row r="35" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B35" s="69" t="s">
+      <c r="D34" s="84"/>
+      <c r="E34" s="84"/>
+      <c r="F34" s="84"/>
+      <c r="G34" s="84"/>
+      <c r="H34" s="84"/>
+      <c r="I34" s="84"/>
+      <c r="J34" s="84"/>
+      <c r="K34" s="84"/>
+      <c r="L34" s="84"/>
+      <c r="M34" s="84"/>
+      <c r="N34" s="84"/>
+      <c r="O34" s="84"/>
+      <c r="P34" s="84"/>
+      <c r="Q34" s="84"/>
+      <c r="R34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="84"/>
+      <c r="V34" s="84"/>
+      <c r="W34" s="84"/>
+      <c r="X34" s="84"/>
+      <c r="Y34" s="84"/>
+      <c r="Z34" s="84"/>
+      <c r="AA34" s="84"/>
+      <c r="AB34" s="84"/>
+    </row>
+    <row r="35" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="67">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B35" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="49" t="s">
+      <c r="C35" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="18"/>
-      <c r="L35" s="18"/>
-      <c r="M35" s="18"/>
-      <c r="N35" s="18"/>
-      <c r="O35" s="18"/>
-      <c r="P35" s="18"/>
-      <c r="Q35" s="18"/>
-      <c r="R35" s="18"/>
-    </row>
-    <row r="36" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B36" s="66"/>
-      <c r="C36" s="50" t="s">
+      <c r="D35" s="83"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="83"/>
+      <c r="G35" s="83"/>
+      <c r="H35" s="83"/>
+      <c r="I35" s="83"/>
+      <c r="J35" s="83"/>
+      <c r="K35" s="83"/>
+      <c r="L35" s="83"/>
+      <c r="M35" s="83"/>
+      <c r="N35" s="83"/>
+      <c r="O35" s="83"/>
+      <c r="P35" s="83"/>
+      <c r="Q35" s="83"/>
+      <c r="R35" s="83"/>
+      <c r="S35" s="83"/>
+      <c r="T35" s="83"/>
+      <c r="U35" s="83"/>
+      <c r="V35" s="83"/>
+      <c r="W35" s="83"/>
+      <c r="X35" s="83"/>
+      <c r="Y35" s="83"/>
+      <c r="Z35" s="83"/>
+      <c r="AA35" s="83"/>
+      <c r="AB35" s="83"/>
+    </row>
+    <row r="36" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B36" s="40"/>
+      <c r="C36" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="45"/>
-      <c r="K36" s="45"/>
-      <c r="L36" s="45"/>
-      <c r="M36" s="45"/>
-      <c r="N36" s="45"/>
-      <c r="O36" s="45"/>
-      <c r="P36" s="45"/>
-      <c r="Q36" s="45"/>
-      <c r="R36" s="45"/>
-    </row>
-    <row r="37" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B37" s="66"/>
-      <c r="C37" s="50" t="s">
+      <c r="D36" s="92"/>
+      <c r="E36" s="92"/>
+      <c r="F36" s="92"/>
+      <c r="G36" s="92"/>
+      <c r="H36" s="92"/>
+      <c r="I36" s="92"/>
+      <c r="J36" s="92"/>
+      <c r="K36" s="92"/>
+      <c r="L36" s="92"/>
+      <c r="M36" s="92"/>
+      <c r="N36" s="92"/>
+      <c r="O36" s="92"/>
+      <c r="P36" s="92"/>
+      <c r="Q36" s="92"/>
+      <c r="R36" s="92"/>
+      <c r="S36" s="92"/>
+      <c r="T36" s="92"/>
+      <c r="U36" s="92"/>
+      <c r="V36" s="92"/>
+      <c r="W36" s="92"/>
+      <c r="X36" s="92"/>
+      <c r="Y36" s="92"/>
+      <c r="Z36" s="92"/>
+      <c r="AA36" s="92"/>
+      <c r="AB36" s="92"/>
+    </row>
+    <row r="37" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B37" s="40"/>
+      <c r="C37" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="45"/>
-      <c r="H37" s="45"/>
-      <c r="I37" s="45"/>
-      <c r="J37" s="45"/>
-      <c r="K37" s="45"/>
-      <c r="L37" s="45"/>
-      <c r="M37" s="45"/>
-      <c r="N37" s="45"/>
-      <c r="O37" s="45"/>
-      <c r="P37" s="45"/>
-      <c r="Q37" s="45"/>
-      <c r="R37" s="45"/>
-    </row>
-    <row r="38" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B38" s="66"/>
-      <c r="C38" s="50" t="s">
+      <c r="D37" s="92"/>
+      <c r="E37" s="92"/>
+      <c r="F37" s="92"/>
+      <c r="G37" s="92"/>
+      <c r="H37" s="92"/>
+      <c r="I37" s="92"/>
+      <c r="J37" s="92"/>
+      <c r="K37" s="92"/>
+      <c r="L37" s="92"/>
+      <c r="M37" s="92"/>
+      <c r="N37" s="92"/>
+      <c r="O37" s="92"/>
+      <c r="P37" s="92"/>
+      <c r="Q37" s="92"/>
+      <c r="R37" s="92"/>
+      <c r="S37" s="92"/>
+      <c r="T37" s="92"/>
+      <c r="U37" s="92"/>
+      <c r="V37" s="92"/>
+      <c r="W37" s="92"/>
+      <c r="X37" s="92"/>
+      <c r="Y37" s="92"/>
+      <c r="Z37" s="92"/>
+      <c r="AA37" s="92"/>
+      <c r="AB37" s="92"/>
+    </row>
+    <row r="38" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B38" s="40"/>
+      <c r="C38" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="D38" s="45"/>
-      <c r="E38" s="45"/>
-      <c r="F38" s="45"/>
-      <c r="G38" s="45"/>
-      <c r="H38" s="45"/>
-      <c r="I38" s="45"/>
-      <c r="J38" s="45"/>
-      <c r="K38" s="45"/>
-      <c r="L38" s="45"/>
-      <c r="M38" s="45"/>
-      <c r="N38" s="45"/>
-      <c r="O38" s="45"/>
-      <c r="P38" s="45"/>
-      <c r="Q38" s="45"/>
-      <c r="R38" s="45"/>
-    </row>
-    <row r="39" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B39" s="66"/>
-      <c r="C39" s="50" t="s">
+      <c r="D38" s="92"/>
+      <c r="E38" s="92"/>
+      <c r="F38" s="92"/>
+      <c r="G38" s="92"/>
+      <c r="H38" s="92"/>
+      <c r="I38" s="92"/>
+      <c r="J38" s="92"/>
+      <c r="K38" s="92"/>
+      <c r="L38" s="92"/>
+      <c r="M38" s="92"/>
+      <c r="N38" s="92"/>
+      <c r="O38" s="92"/>
+      <c r="P38" s="92"/>
+      <c r="Q38" s="92"/>
+      <c r="R38" s="92"/>
+      <c r="S38" s="92"/>
+      <c r="T38" s="92"/>
+      <c r="U38" s="92"/>
+      <c r="V38" s="92"/>
+      <c r="W38" s="92"/>
+      <c r="X38" s="92"/>
+      <c r="Y38" s="92"/>
+      <c r="Z38" s="92"/>
+      <c r="AA38" s="92"/>
+      <c r="AB38" s="92"/>
+    </row>
+    <row r="39" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B39" s="40"/>
+      <c r="C39" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D39" s="45"/>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="45"/>
-      <c r="I39" s="45"/>
-      <c r="J39" s="45"/>
-      <c r="K39" s="45"/>
-      <c r="L39" s="45"/>
-      <c r="M39" s="45"/>
-      <c r="N39" s="45"/>
-      <c r="O39" s="45"/>
-      <c r="P39" s="45"/>
-      <c r="Q39" s="45"/>
-      <c r="R39" s="45"/>
-    </row>
-    <row r="40" spans="1:18" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B40" s="67"/>
-      <c r="C40" s="51" t="s">
+      <c r="D39" s="92"/>
+      <c r="E39" s="92"/>
+      <c r="F39" s="92"/>
+      <c r="G39" s="92"/>
+      <c r="H39" s="92"/>
+      <c r="I39" s="92"/>
+      <c r="J39" s="92"/>
+      <c r="K39" s="92"/>
+      <c r="L39" s="92"/>
+      <c r="M39" s="92"/>
+      <c r="N39" s="92"/>
+      <c r="O39" s="92"/>
+      <c r="P39" s="92"/>
+      <c r="Q39" s="92"/>
+      <c r="R39" s="92"/>
+      <c r="S39" s="92"/>
+      <c r="T39" s="92"/>
+      <c r="U39" s="92"/>
+      <c r="V39" s="92"/>
+      <c r="W39" s="92"/>
+      <c r="X39" s="92"/>
+      <c r="Y39" s="92"/>
+      <c r="Z39" s="92"/>
+      <c r="AA39" s="92"/>
+      <c r="AB39" s="92"/>
+    </row>
+    <row r="40" spans="1:28" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="68">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B40" s="43"/>
+      <c r="C40" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="21"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
-      <c r="M40" s="21"/>
-      <c r="N40" s="21"/>
-      <c r="O40" s="21"/>
-      <c r="P40" s="21"/>
-      <c r="Q40" s="21"/>
-      <c r="R40" s="21"/>
-    </row>
-    <row r="41" spans="1:18" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="52">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B41" s="53" t="s">
+      <c r="D40" s="84"/>
+      <c r="E40" s="84"/>
+      <c r="F40" s="84"/>
+      <c r="G40" s="84"/>
+      <c r="H40" s="84"/>
+      <c r="I40" s="84"/>
+      <c r="J40" s="84"/>
+      <c r="K40" s="84"/>
+      <c r="L40" s="84"/>
+      <c r="M40" s="84"/>
+      <c r="N40" s="84"/>
+      <c r="O40" s="84"/>
+      <c r="P40" s="84"/>
+      <c r="Q40" s="84"/>
+      <c r="R40" s="84"/>
+      <c r="S40" s="84"/>
+      <c r="T40" s="84"/>
+      <c r="U40" s="84"/>
+      <c r="V40" s="84"/>
+      <c r="W40" s="84"/>
+      <c r="X40" s="84"/>
+      <c r="Y40" s="84"/>
+      <c r="Z40" s="84"/>
+      <c r="AA40" s="84"/>
+      <c r="AB40" s="84"/>
+    </row>
+    <row r="41" spans="1:28" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B41" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="54" t="s">
+      <c r="C41" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="55"/>
-      <c r="H41" s="55"/>
-      <c r="I41" s="55"/>
-      <c r="J41" s="55"/>
-      <c r="K41" s="55"/>
-      <c r="L41" s="55"/>
-      <c r="M41" s="55"/>
-      <c r="N41" s="55"/>
-      <c r="O41" s="55"/>
-      <c r="P41" s="55"/>
-      <c r="Q41" s="55"/>
-      <c r="R41" s="55"/>
-    </row>
-    <row r="42" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B42" s="69" t="s">
+      <c r="D41" s="94"/>
+      <c r="E41" s="94"/>
+      <c r="F41" s="94"/>
+      <c r="G41" s="94"/>
+      <c r="H41" s="94"/>
+      <c r="I41" s="94"/>
+      <c r="J41" s="94"/>
+      <c r="K41" s="94"/>
+      <c r="L41" s="94"/>
+      <c r="M41" s="94"/>
+      <c r="N41" s="94"/>
+      <c r="O41" s="94"/>
+      <c r="P41" s="94"/>
+      <c r="Q41" s="94"/>
+      <c r="R41" s="94"/>
+      <c r="S41" s="94"/>
+      <c r="T41" s="94"/>
+      <c r="U41" s="94"/>
+      <c r="V41" s="94"/>
+      <c r="W41" s="94"/>
+      <c r="X41" s="94"/>
+      <c r="Y41" s="94"/>
+      <c r="Z41" s="94"/>
+      <c r="AA41" s="94"/>
+      <c r="AB41" s="94"/>
+    </row>
+    <row r="42" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="67">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B42" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="18"/>
-      <c r="K42" s="18"/>
-      <c r="L42" s="18"/>
-      <c r="M42" s="18"/>
-      <c r="N42" s="18"/>
-      <c r="O42" s="18"/>
-      <c r="P42" s="18"/>
-      <c r="Q42" s="18"/>
-      <c r="R42" s="18"/>
-    </row>
-    <row r="43" spans="1:18" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B43" s="67"/>
-      <c r="C43" s="20" t="s">
+      <c r="D42" s="83"/>
+      <c r="E42" s="83"/>
+      <c r="F42" s="83"/>
+      <c r="G42" s="83"/>
+      <c r="H42" s="83"/>
+      <c r="I42" s="83"/>
+      <c r="J42" s="83"/>
+      <c r="K42" s="83"/>
+      <c r="L42" s="83"/>
+      <c r="M42" s="83"/>
+      <c r="N42" s="83"/>
+      <c r="O42" s="83"/>
+      <c r="P42" s="83"/>
+      <c r="Q42" s="83"/>
+      <c r="R42" s="83"/>
+      <c r="S42" s="83"/>
+      <c r="T42" s="83"/>
+      <c r="U42" s="83"/>
+      <c r="V42" s="83"/>
+      <c r="W42" s="83"/>
+      <c r="X42" s="83"/>
+      <c r="Y42" s="83"/>
+      <c r="Z42" s="83"/>
+      <c r="AA42" s="83"/>
+      <c r="AB42" s="83"/>
+    </row>
+    <row r="43" spans="1:28" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="68">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B43" s="43"/>
+      <c r="C43" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="21"/>
-      <c r="J43" s="21"/>
-      <c r="K43" s="21"/>
-      <c r="L43" s="21"/>
-      <c r="M43" s="21"/>
-      <c r="N43" s="21"/>
-      <c r="O43" s="21"/>
-      <c r="P43" s="21"/>
-      <c r="Q43" s="21"/>
-      <c r="R43" s="21"/>
-    </row>
-    <row r="44" spans="1:18" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B44" s="56" t="s">
+      <c r="D43" s="84"/>
+      <c r="E43" s="84"/>
+      <c r="F43" s="84"/>
+      <c r="G43" s="84"/>
+      <c r="H43" s="84"/>
+      <c r="I43" s="84"/>
+      <c r="J43" s="84"/>
+      <c r="K43" s="84"/>
+      <c r="L43" s="84"/>
+      <c r="M43" s="84"/>
+      <c r="N43" s="84"/>
+      <c r="O43" s="84"/>
+      <c r="P43" s="84"/>
+      <c r="Q43" s="84"/>
+      <c r="R43" s="84"/>
+      <c r="S43" s="84"/>
+      <c r="T43" s="84"/>
+      <c r="U43" s="84"/>
+      <c r="V43" s="84"/>
+      <c r="W43" s="84"/>
+      <c r="X43" s="84"/>
+      <c r="Y43" s="84"/>
+      <c r="Z43" s="84"/>
+      <c r="AA43" s="84"/>
+      <c r="AB43" s="84"/>
+    </row>
+    <row r="44" spans="1:28" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="68">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B44" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="C44" s="20" t="s">
+      <c r="C44" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21"/>
-      <c r="G44" s="21"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="21"/>
-      <c r="J44" s="21"/>
-      <c r="K44" s="21"/>
-      <c r="L44" s="21"/>
-      <c r="M44" s="21"/>
-      <c r="N44" s="21"/>
-      <c r="O44" s="21"/>
-      <c r="P44" s="21"/>
-      <c r="Q44" s="21"/>
-      <c r="R44" s="21"/>
-    </row>
-    <row r="45" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B45" s="79" t="s">
+      <c r="D44" s="84"/>
+      <c r="E44" s="84"/>
+      <c r="F44" s="84"/>
+      <c r="G44" s="84"/>
+      <c r="H44" s="84"/>
+      <c r="I44" s="84"/>
+      <c r="J44" s="84"/>
+      <c r="K44" s="84"/>
+      <c r="L44" s="84"/>
+      <c r="M44" s="84"/>
+      <c r="N44" s="84"/>
+      <c r="O44" s="84"/>
+      <c r="P44" s="84"/>
+      <c r="Q44" s="84"/>
+      <c r="R44" s="84"/>
+      <c r="S44" s="84"/>
+      <c r="T44" s="84"/>
+      <c r="U44" s="84"/>
+      <c r="V44" s="84"/>
+      <c r="W44" s="84"/>
+      <c r="X44" s="84"/>
+      <c r="Y44" s="84"/>
+      <c r="Z44" s="84"/>
+      <c r="AA44" s="84"/>
+      <c r="AB44" s="84"/>
+    </row>
+    <row r="45" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="67">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B45" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C45" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
-      <c r="J45" s="18"/>
-      <c r="K45" s="18"/>
-      <c r="L45" s="18"/>
-      <c r="M45" s="18"/>
-      <c r="N45" s="18"/>
-      <c r="O45" s="18"/>
-      <c r="P45" s="18"/>
-      <c r="Q45" s="18"/>
-      <c r="R45" s="18"/>
-    </row>
-    <row r="46" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B46" s="66"/>
-      <c r="C46" s="44" t="s">
+      <c r="D45" s="83"/>
+      <c r="E45" s="83"/>
+      <c r="F45" s="83"/>
+      <c r="G45" s="83"/>
+      <c r="H45" s="83"/>
+      <c r="I45" s="83"/>
+      <c r="J45" s="83"/>
+      <c r="K45" s="83"/>
+      <c r="L45" s="83"/>
+      <c r="M45" s="83"/>
+      <c r="N45" s="83"/>
+      <c r="O45" s="83"/>
+      <c r="P45" s="83"/>
+      <c r="Q45" s="83"/>
+      <c r="R45" s="83"/>
+      <c r="S45" s="83"/>
+      <c r="T45" s="83"/>
+      <c r="U45" s="83"/>
+      <c r="V45" s="83"/>
+      <c r="W45" s="83"/>
+      <c r="X45" s="83"/>
+      <c r="Y45" s="83"/>
+      <c r="Z45" s="83"/>
+      <c r="AA45" s="83"/>
+      <c r="AB45" s="83"/>
+    </row>
+    <row r="46" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B46" s="40"/>
+      <c r="C46" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D46" s="45"/>
-      <c r="E46" s="45"/>
-      <c r="F46" s="45"/>
-      <c r="G46" s="45"/>
-      <c r="H46" s="45"/>
-      <c r="I46" s="45"/>
-      <c r="J46" s="45"/>
-      <c r="K46" s="45"/>
-      <c r="L46" s="45"/>
-      <c r="M46" s="45"/>
-      <c r="N46" s="45"/>
-      <c r="O46" s="45"/>
-      <c r="P46" s="45"/>
-      <c r="Q46" s="45"/>
-      <c r="R46" s="45"/>
-    </row>
-    <row r="47" spans="1:18" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B47" s="66"/>
-      <c r="C47" s="44" t="s">
+      <c r="D46" s="92"/>
+      <c r="E46" s="92"/>
+      <c r="F46" s="92"/>
+      <c r="G46" s="92"/>
+      <c r="H46" s="92"/>
+      <c r="I46" s="92"/>
+      <c r="J46" s="92"/>
+      <c r="K46" s="92"/>
+      <c r="L46" s="92"/>
+      <c r="M46" s="92"/>
+      <c r="N46" s="92"/>
+      <c r="O46" s="92"/>
+      <c r="P46" s="92"/>
+      <c r="Q46" s="92"/>
+      <c r="R46" s="92"/>
+      <c r="S46" s="92"/>
+      <c r="T46" s="92"/>
+      <c r="U46" s="92"/>
+      <c r="V46" s="92"/>
+      <c r="W46" s="92"/>
+      <c r="X46" s="92"/>
+      <c r="Y46" s="92"/>
+      <c r="Z46" s="92"/>
+      <c r="AA46" s="92"/>
+      <c r="AB46" s="92"/>
+    </row>
+    <row r="47" spans="1:28" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B47" s="40"/>
+      <c r="C47" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="15"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
-      <c r="M47" s="15"/>
-      <c r="N47" s="15"/>
-      <c r="O47" s="15"/>
-      <c r="P47" s="15"/>
-      <c r="Q47" s="15"/>
-      <c r="R47" s="15"/>
-    </row>
-    <row r="48" spans="1:18" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="B48" s="66"/>
-      <c r="C48" s="14" t="s">
+      <c r="D47" s="82"/>
+      <c r="E47" s="82"/>
+      <c r="F47" s="82"/>
+      <c r="G47" s="82"/>
+      <c r="H47" s="82"/>
+      <c r="I47" s="82"/>
+      <c r="J47" s="82"/>
+      <c r="K47" s="82"/>
+      <c r="L47" s="82"/>
+      <c r="M47" s="82"/>
+      <c r="N47" s="82"/>
+      <c r="O47" s="82"/>
+      <c r="P47" s="82"/>
+      <c r="Q47" s="82"/>
+      <c r="R47" s="82"/>
+      <c r="S47" s="82"/>
+      <c r="T47" s="82"/>
+      <c r="U47" s="82"/>
+      <c r="V47" s="82"/>
+      <c r="W47" s="82"/>
+      <c r="X47" s="82"/>
+      <c r="Y47" s="82"/>
+      <c r="Z47" s="82"/>
+      <c r="AA47" s="82"/>
+      <c r="AB47" s="82"/>
+    </row>
+    <row r="48" spans="1:28" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="68">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B48" s="40"/>
+      <c r="C48" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D48" s="57"/>
-      <c r="E48" s="57"/>
-      <c r="F48" s="57"/>
-      <c r="G48" s="57"/>
-      <c r="H48" s="57"/>
-      <c r="I48" s="57"/>
-      <c r="J48" s="57"/>
-      <c r="K48" s="57"/>
-      <c r="L48" s="57"/>
-      <c r="M48" s="57"/>
-      <c r="N48" s="57"/>
-      <c r="O48" s="57"/>
-      <c r="P48" s="57"/>
-      <c r="Q48" s="57"/>
-      <c r="R48" s="57"/>
-    </row>
-    <row r="49" spans="1:18" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="58"/>
-      <c r="B49" s="59" t="s">
+      <c r="D48" s="95"/>
+      <c r="E48" s="95"/>
+      <c r="F48" s="95"/>
+      <c r="G48" s="95"/>
+      <c r="H48" s="95"/>
+      <c r="I48" s="95"/>
+      <c r="J48" s="95"/>
+      <c r="K48" s="95"/>
+      <c r="L48" s="95"/>
+      <c r="M48" s="95"/>
+      <c r="N48" s="95"/>
+      <c r="O48" s="95"/>
+      <c r="P48" s="95"/>
+      <c r="Q48" s="95"/>
+      <c r="R48" s="95"/>
+      <c r="S48" s="95"/>
+      <c r="T48" s="95"/>
+      <c r="U48" s="95"/>
+      <c r="V48" s="95"/>
+      <c r="W48" s="95"/>
+      <c r="X48" s="95"/>
+      <c r="Y48" s="95"/>
+      <c r="Z48" s="95"/>
+      <c r="AA48" s="95"/>
+      <c r="AB48" s="95"/>
+    </row>
+    <row r="49" spans="1:28" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="79"/>
+      <c r="B49" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C49" s="60" t="s">
+      <c r="C49" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="D49" s="61"/>
-      <c r="E49" s="61"/>
-      <c r="F49" s="61"/>
-      <c r="G49" s="61"/>
-      <c r="H49" s="61"/>
-      <c r="I49" s="61"/>
-      <c r="J49" s="61"/>
-      <c r="K49" s="61"/>
-      <c r="L49" s="61"/>
-      <c r="M49" s="61"/>
-      <c r="N49" s="61"/>
-      <c r="O49" s="61"/>
-      <c r="P49" s="61"/>
-      <c r="Q49" s="61"/>
-      <c r="R49" s="61"/>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A50" s="62"/>
-      <c r="B50" s="62"/>
-      <c r="C50" s="62"/>
-      <c r="D50" s="62"/>
-      <c r="E50" s="62"/>
-      <c r="F50" s="62"/>
-      <c r="G50" s="62"/>
-      <c r="H50" s="62"/>
-      <c r="I50" s="62"/>
-      <c r="J50" s="62"/>
-      <c r="K50" s="62"/>
-      <c r="L50" s="62"/>
-      <c r="M50" s="62"/>
-      <c r="N50" s="62"/>
-      <c r="O50" s="62"/>
-      <c r="P50" s="62"/>
-      <c r="Q50" s="62"/>
-      <c r="R50" s="62"/>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A51" s="62"/>
-      <c r="B51" s="62"/>
-      <c r="C51" s="62"/>
-      <c r="D51" s="62"/>
-      <c r="E51" s="62"/>
-      <c r="F51" s="62"/>
-      <c r="G51" s="62"/>
-      <c r="H51" s="62"/>
-      <c r="I51" s="62"/>
-      <c r="J51" s="62"/>
-      <c r="K51" s="62"/>
-      <c r="L51" s="62"/>
-      <c r="M51" s="62"/>
-      <c r="N51" s="62"/>
-      <c r="O51" s="62"/>
-      <c r="P51" s="62"/>
-      <c r="Q51" s="62"/>
-      <c r="R51" s="62"/>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A52" s="62"/>
-      <c r="B52" s="62"/>
-      <c r="C52" s="62"/>
-      <c r="D52" s="62"/>
-      <c r="E52" s="62"/>
-      <c r="F52" s="62"/>
-      <c r="G52" s="62"/>
-      <c r="H52" s="62"/>
-      <c r="I52" s="62"/>
-      <c r="J52" s="62"/>
-      <c r="K52" s="62"/>
-      <c r="L52" s="62"/>
-      <c r="M52" s="62"/>
-      <c r="N52" s="62"/>
-      <c r="O52" s="62"/>
-      <c r="P52" s="62"/>
-      <c r="Q52" s="62"/>
-      <c r="R52" s="62"/>
+      <c r="D49" s="96"/>
+      <c r="E49" s="96"/>
+      <c r="F49" s="96"/>
+      <c r="G49" s="96"/>
+      <c r="H49" s="96"/>
+      <c r="I49" s="96"/>
+      <c r="J49" s="96"/>
+      <c r="K49" s="96"/>
+      <c r="L49" s="96"/>
+      <c r="M49" s="96"/>
+      <c r="N49" s="96"/>
+      <c r="O49" s="96"/>
+      <c r="P49" s="96"/>
+      <c r="Q49" s="96"/>
+      <c r="R49" s="96"/>
+      <c r="S49" s="96"/>
+      <c r="T49" s="96"/>
+      <c r="U49" s="96"/>
+      <c r="V49" s="96"/>
+      <c r="W49" s="96"/>
+      <c r="X49" s="96"/>
+      <c r="Y49" s="96"/>
+      <c r="Z49" s="96"/>
+      <c r="AA49" s="96"/>
+      <c r="AB49" s="96"/>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A50" s="28"/>
+      <c r="B50" s="28"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="28"/>
+      <c r="J50" s="28"/>
+      <c r="K50" s="28"/>
+      <c r="L50" s="28"/>
+      <c r="M50" s="28"/>
+      <c r="N50" s="28"/>
+      <c r="O50" s="28"/>
+      <c r="P50" s="28"/>
+      <c r="Q50" s="28"/>
+      <c r="R50" s="28"/>
+      <c r="S50" s="28"/>
+      <c r="T50" s="28"/>
+      <c r="U50" s="28"/>
+      <c r="V50" s="28"/>
+      <c r="W50" s="28"/>
+      <c r="X50" s="28"/>
+      <c r="Y50" s="28"/>
+      <c r="Z50" s="28"/>
+      <c r="AA50" s="28"/>
+      <c r="AB50" s="28"/>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A51" s="28"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="28"/>
+      <c r="K51" s="28"/>
+      <c r="L51" s="28"/>
+      <c r="M51" s="28"/>
+      <c r="N51" s="28"/>
+      <c r="O51" s="28"/>
+      <c r="P51" s="28"/>
+      <c r="Q51" s="28"/>
+      <c r="R51" s="28"/>
+      <c r="S51" s="28"/>
+      <c r="T51" s="28"/>
+      <c r="U51" s="28"/>
+      <c r="V51" s="28"/>
+      <c r="W51" s="28"/>
+      <c r="X51" s="28"/>
+      <c r="Y51" s="28"/>
+      <c r="Z51" s="28"/>
+      <c r="AA51" s="28"/>
+      <c r="AB51" s="28"/>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A52" s="28"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="28"/>
+      <c r="R52" s="28"/>
+      <c r="S52" s="28"/>
+      <c r="T52" s="28"/>
+      <c r="U52" s="28"/>
+      <c r="V52" s="28"/>
+      <c r="W52" s="28"/>
+      <c r="X52" s="28"/>
+      <c r="Y52" s="28"/>
+      <c r="Z52" s="28"/>
+      <c r="AA52" s="28"/>
+      <c r="AB52" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="B45:B48"/>
@@ -3065,12 +3603,6 @@
     <mergeCell ref="B31:B34"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
